--- a/3-需求跟踪矩阵建立/缺陷记录.xlsx
+++ b/3-需求跟踪矩阵建立/缺陷记录.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -752,7 +752,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>可用（注：团队实测为 17）</t>
+          <t>可用；2026-10-23 实测 37/37 JUnit 通过</t>
         </is>
       </c>
     </row>
@@ -973,6 +973,28 @@
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t>缺陷已登记</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>自动化测试</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>mvn -B test（IDEA 内置 Maven 3.9.11，JDK 21）</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Tests run: 37, Failures: 0, Errors: 0, Skipped: 0；BUILD SUCCESS；H2 内存库</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
     </row>

--- a/3-需求跟踪矩阵建立/缺陷记录.xlsx
+++ b/3-需求跟踪矩阵建立/缺陷记录.xlsx
@@ -984,12 +984,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>mvn -B test（IDEA 内置 Maven 3.9.11，JDK 21）</t>
+          <t>mvn -B test（IDEA 内置 Maven 3.9.11，JDK 21）；含 QA 新增 14 个测试</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Tests run: 37, Failures: 0, Errors: 0, Skipped: 0；BUILD SUCCESS；H2 内存库</t>
+          <t>Tests run: 51, Failures: 0, Errors: 0, Skipped: 0；BUILD SUCCESS；H2 内存库</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">

--- a/3-需求跟踪矩阵建立/缺陷记录.xlsx
+++ b/3-需求跟踪矩阵建立/缺陷记录.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -998,6 +998,138 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MySQL 独立实例</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>mysqld --initialize-insecure --datadir=D:\mysql_qa_data --port=3308</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>MySQL 8.4.4，库 library_dev，5 张表 + renew_count 迁移完成</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>应用实例（真库）</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>java -jar library-process-dev-1.0.0-SNAPSHOT.jar（demo profile）</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:8081，health 200，10 位演示读者与 4 本样例图书已初始化</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>接口层实测</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>17 项场景（登录/CSRF/借还/续借/检索/管理接口/CSV/日志/权限）</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>17 项全部通过</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>真库并发</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>scripts/mysql-concurrency-test.py（10 线程争抢 BC-CONC-001）</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>success=1，其余 9 个 409 BOOK_UNAVAILABLE，无双重借出</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>借还响应时间</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>20 次借还请求计时</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>平均 15.8ms，P95=22ms，最大 24ms（限值 2000ms）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>数据库一致性</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>sql/04_verify_consistency.sql</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>四类不一致查询全部 0 行</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
